--- a/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
+++ b/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BDTPTUMCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\BDTPTUMCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C9E189-3181-4F0B-B84A-E9F8F95A04A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8446E642-D5F1-495A-9F7D-F6B45EF2F3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="12645" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="BDTPTUMCF" sheetId="2" r:id="rId2"/>
+    <sheet name="About" sheetId="12" r:id="rId1"/>
+    <sheet name="BDTPTUMCF" sheetId="21" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
@@ -35,6 +35,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -43,7 +46,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -51,87 +53,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>natural gas nonpeaker</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>solar pv</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geothermal </t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: </t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (peak time capacity factors)</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>None needed</t>
+  </si>
+  <si>
+    <t>This file selects whether a plant type will use the maximum capacity factors set in the elec/MCF</t>
+  </si>
+  <si>
+    <t>file or hourly capacity factors set in the elec/SYSHECF file for the maximum</t>
+  </si>
+  <si>
+    <t>amount it can dispatch in any given hour. Generally, variable sources</t>
+  </si>
+  <si>
+    <t>of electricity like wind and solar should not use maximum capacity factors.</t>
+  </si>
   <si>
     <t>BDTPTUMCF Boolean Does This Plant Type Use Maximum Capacity Factor</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: </t>
-  </si>
-  <si>
-    <t>None needed</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>This file selects whether a plant type will use the maximum capacity factors set in the elec/MCF</t>
-  </si>
-  <si>
-    <t>file or hourly capacity factors set in the elec/SYSHECF file for the maximum</t>
-  </si>
-  <si>
-    <t>amount it can dispatch in any given hour. Generally, variable sources</t>
-  </si>
-  <si>
-    <t>of electricity like wind and solar should not use maximum capacity factors.</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (peak time capacity factors)</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>solar pv</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geothermal </t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>natural gas nonpeaker</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>offshore wind</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
   </si>
   <si>
     <t>hard coal w CCS</t>
@@ -294,25 +293,25 @@
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -338,17 +337,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="11">
-    <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Footnotes: top row" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Footnotes: top row" xfId="8" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Header: bottom row" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Normal 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Parent row" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Percent 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Table title" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Parent row" xfId="7" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Percent 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Table title" xfId="3" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -767,10 +766,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -778,10 +774,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1"/>
       <c r="H3" s="1"/>
@@ -791,46 +787,46 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="A22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A22" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Summer, Winter"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
@@ -841,16 +837,16 @@
     <col min="2" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="8">
         <v>1</v>
@@ -859,7 +855,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8">
         <v>1</v>
@@ -868,7 +864,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B4" s="8">
         <v>1</v>
@@ -877,7 +873,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>0</v>
@@ -886,7 +882,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B6" s="8">
         <v>0</v>
@@ -895,7 +891,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" s="8">
         <v>0</v>
@@ -904,7 +900,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B8" s="8">
         <v>0</v>
@@ -913,7 +909,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B9" s="8">
         <v>0</v>
@@ -922,7 +918,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
@@ -931,7 +927,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B11" s="8">
         <v>0</v>
@@ -940,7 +936,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B12" s="8">
         <v>1</v>
@@ -949,7 +945,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="B13" s="8">
         <v>1</v>
@@ -958,7 +954,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B14" s="8">
         <v>1</v>
@@ -967,7 +963,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B15" s="8">
         <v>0</v>
@@ -976,7 +972,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B16" s="8">
         <v>1</v>
@@ -985,7 +981,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B17" s="8">
         <v>1</v>
@@ -994,7 +990,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
@@ -1003,7 +999,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="9">
         <f>B2</f>
@@ -1012,7 +1008,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="9">
         <f>B4</f>
@@ -1021,7 +1017,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="9">
         <f>B10</f>
@@ -1030,7 +1026,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="9">
         <f>B14</f>
@@ -1039,7 +1035,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="9">
         <f>B5</f>
@@ -1048,7 +1044,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="8">
         <v>1</v>
@@ -1056,7 +1052,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25">
         <v>1</v>

--- a/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
+++ b/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BDTPTUMCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\IA\elec\BDTPTUMCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EBF1DD1-D0C8-49CB-817B-BBEC76D1BAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E17A1D55-8AE1-4241-8D7C-7C93AE99E8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="1890" windowWidth="14700" windowHeight="12645" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -369,6 +369,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Header Descriptions"/>
       <sheetName val="2019 NQC List"/>
@@ -390,6 +393,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Information"/>
       <sheetName val="Request Type 1-2"/>
@@ -760,15 +766,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.5703125" customWidth="1"/>
-    <col min="8" max="8" width="53.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.265625" customWidth="1"/>
+    <col min="2" max="2" width="50.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.59765625" customWidth="1"/>
+    <col min="8" max="8" width="53.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -776,13 +782,13 @@
         <v>33</v>
       </c>
       <c r="C1" s="11">
-        <v>45484</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -792,34 +798,34 @@
       <c r="E3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -841,20 +847,20 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" customWidth="1"/>
+    <col min="1" max="1" width="35.59765625" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -863,7 +869,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -872,7 +878,7 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -881,7 +887,7 @@
       </c>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -890,7 +896,7 @@
       </c>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -899,7 +905,7 @@
       </c>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -908,7 +914,7 @@
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -917,7 +923,7 @@
       </c>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -926,7 +932,7 @@
       </c>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -935,7 +941,7 @@
       </c>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -944,7 +950,7 @@
       </c>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -953,7 +959,7 @@
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -962,7 +968,7 @@
       </c>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -971,7 +977,7 @@
       </c>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -980,7 +986,7 @@
       </c>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -989,7 +995,7 @@
       </c>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -998,7 +1004,7 @@
       </c>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1007,7 +1013,7 @@
       </c>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1016,7 +1022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1025,7 +1031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1034,7 +1040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1043,7 +1049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1052,7 +1058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="10" t="s">
         <v>31</v>
       </c>
@@ -1060,7 +1066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" s="10" t="s">
         <v>32</v>
       </c>
